--- a/Google/salary_summary.xlsx
+++ b/Google/salary_summary.xlsx
@@ -8,23 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e3de5047e933f7b4/Pet Wealth/Analytics/Python_script/Google/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_5E45769F5B90DC3AA334CE73565ED87656CEAE23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB25CB5-2E55-4926-A984-7A467C889E3E}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_4AA955815B50DB295F76DA73565ED87656CE1E5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C0D2364-1876-49D6-A915-74109BAD9806}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId3"/>
-  </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="288">
   <si>
     <t>shift_uuid</t>
   </si>
@@ -888,30 +884,6 @@
   </si>
   <si>
     <t>d1dcbee90b1947b987b371b32c583af3</t>
-  </si>
-  <si>
-    <t>Названия строк</t>
-  </si>
-  <si>
-    <t>Общий итог</t>
-  </si>
-  <si>
-    <t>Сумма по полю ВсьогоЗаЗміну</t>
-  </si>
-  <si>
-    <t>Количество по полю shift_uuid</t>
-  </si>
-  <si>
-    <t>Сумма по полю Ставка</t>
-  </si>
-  <si>
-    <t>Сумма по полю КолективнаПремія_Всього</t>
-  </si>
-  <si>
-    <t>Сумма по полю КолективнаПремія_Зоомагазин</t>
-  </si>
-  <si>
-    <t>Сумма по полю КолективнаПремія_Послуги</t>
   </si>
 </sst>
 </file>
@@ -968,34 +940,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <b/>
@@ -1054,4636 +1009,32 @@
 </styleSheet>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Алексей Лёдин" refreshedDate="45812.075248148147" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="242" xr:uid="{FD73BC71-D490-4716-81D1-DB83E39AEB3A}">
-  <cacheSource type="worksheet">
-    <worksheetSource name="Таблица1"/>
-  </cacheSource>
-  <cacheFields count="16">
-    <cacheField name="shift_uuid" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Прізвище" numFmtId="0">
-      <sharedItems count="18">
-        <s v="Пилипчук Д."/>
-        <s v="Корзаченко О."/>
-        <s v="Прийма Л."/>
-        <s v="Жиліна В."/>
-        <s v="Малахова В."/>
-        <s v="Менько Г."/>
-        <s v="Неткачова А."/>
-        <s v="Конюхова В."/>
-        <s v="Ярославцева Є."/>
-        <s v="Льодін О."/>
-        <s v="Воробей С."/>
-        <s v="Столярова В."/>
-        <s v="Кузнєцова Е."/>
-        <s v="Жиров П."/>
-        <s v="Коржевська С."/>
-        <s v="Литвин В."/>
-        <s v="Касяненко Д."/>
-        <s v="Матрьончик М."/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="ДатаЗміни" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-05-01T00:00:00" maxDate="2025-06-01T00:00:00"/>
-    </cacheField>
-    <cacheField name="Посада" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Відділення" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="ТипЗміни" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="ТривалістьЗміни" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Ставка" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2300"/>
-    </cacheField>
-    <cacheField name="Премія_Зоомагазин" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6.8384999999999998"/>
-    </cacheField>
-    <cacheField name="Премія_Медикаменти" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="45"/>
-    </cacheField>
-    <cacheField name="Премія_Послуги" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="46.109200000000001"/>
-    </cacheField>
-    <cacheField name="Премія_Всього" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="55.859200000000001"/>
-    </cacheField>
-    <cacheField name="КолективнаПремія_Зоомагазин" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="816.46"/>
-    </cacheField>
-    <cacheField name="КолективнаПремія_Послуги" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="3120.41"/>
-    </cacheField>
-    <cacheField name="КолективнаПремія_Всього" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="3936.87"/>
-    </cacheField>
-    <cacheField name="ВсьогоЗаЗміну" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="4936.87"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="242">
-  <r>
-    <s v="816622febdc84324abde3924fe052d3d"/>
-    <x v="0"/>
-    <d v="2025-05-01T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="7b842aff1a8465ad39dd35db4b1c1163"/>
-    <x v="1"/>
-    <d v="2025-05-01T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="c17c61f5da1a2cadbd7b92a086701c98"/>
-    <x v="2"/>
-    <d v="2025-05-01T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="9ba8d833b373483db2e273f4f82cd759"/>
-    <x v="3"/>
-    <d v="2025-05-01T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="c93ae0cf80030ae410b34872454cd3e0"/>
-    <x v="4"/>
-    <d v="2025-05-01T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="339c75a992fa088f1d5fc21006aea406"/>
-    <x v="4"/>
-    <d v="2025-05-01T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="1b7c3428c814cd550b428ecf5d7ed426"/>
-    <x v="5"/>
-    <d v="2025-05-01T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Стоматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <s v="f399876b36b2d9464073eef6f4aa28d1"/>
-    <x v="6"/>
-    <d v="2025-05-01T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="208.34"/>
-    <n v="2501.23"/>
-    <n v="2709.57"/>
-    <n v="3709.57"/>
-  </r>
-  <r>
-    <s v="b57bd33da5048440f387009c77812498"/>
-    <x v="0"/>
-    <d v="2025-05-02T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="2a8528fc01b16959d6b128fe8ddaae7d"/>
-    <x v="7"/>
-    <d v="2025-05-02T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="7def9b0b94384e02fc7798cf4c8741eb"/>
-    <x v="8"/>
-    <d v="2025-05-02T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="0012cc405cc83f3d428e6445385698f4"/>
-    <x v="5"/>
-    <d v="2025-05-02T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="bcb1369445b5f048365680b24c0aa2d7"/>
-    <x v="9"/>
-    <d v="2025-05-02T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="aae3ad11e19394ae753b5bbfec56ef38"/>
-    <x v="9"/>
-    <d v="2025-05-02T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="7951edc1af27db5a4b79188bf55a6aee"/>
-    <x v="10"/>
-    <d v="2025-05-02T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="223.37"/>
-    <n v="873.83"/>
-    <n v="1097.2"/>
-    <n v="2097.1999999999998"/>
-  </r>
-  <r>
-    <s v="9040ba7ca60f444f2312711b55fef3c2"/>
-    <x v="8"/>
-    <d v="2025-05-03T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="be9ed97a362c0b7e0b4f1697e26f2924"/>
-    <x v="11"/>
-    <d v="2025-05-03T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="a678f85b2a748c01bc939c6c2ece66d1"/>
-    <x v="12"/>
-    <d v="2025-05-03T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="5b9264cb964730c2c1df2791668f30fd"/>
-    <x v="12"/>
-    <d v="2025-05-03T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="0599903263d41ef57e4c4735192a4361"/>
-    <x v="3"/>
-    <d v="2025-05-03T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="bdc111332095a92a20f554fe600e1675"/>
-    <x v="13"/>
-    <d v="2025-05-03T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="e1e8b48d3b1d0ab65e878223331e1124"/>
-    <x v="13"/>
-    <d v="2025-05-03T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="363d234cbcc0d896f82345b1689d2c0e"/>
-    <x v="5"/>
-    <d v="2025-05-03T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Стоматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="1.4065000000000001"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1.4065000000000001"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1.4065000000000001"/>
-  </r>
-  <r>
-    <s v="596a467b792008516100aa60542a63bc"/>
-    <x v="14"/>
-    <d v="2025-05-03T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Дерматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="9.75"/>
-    <n v="46.109200000000001"/>
-    <n v="55.859200000000001"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="55.859200000000001"/>
-  </r>
-  <r>
-    <s v="8f29e894acb19bc95cafbf4184d84e09"/>
-    <x v="10"/>
-    <d v="2025-05-03T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="460.33"/>
-    <n v="1625.28"/>
-    <n v="2085.61"/>
-    <n v="3085.61"/>
-  </r>
-  <r>
-    <s v="e676d89aae9f500090ab149188844fde"/>
-    <x v="0"/>
-    <d v="2025-05-04T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="f56727b97d2850880a1fc89c8ae980a9"/>
-    <x v="2"/>
-    <d v="2025-05-04T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="96ec7b5e883e472b319b7a09dfd0f3a0"/>
-    <x v="15"/>
-    <d v="2025-05-04T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="39dd8935776ba6f5f7ec71e8382c5c72"/>
-    <x v="5"/>
-    <d v="2025-05-04T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="6e4d5832bf6c5cdc36136ede58d795c7"/>
-    <x v="4"/>
-    <d v="2025-05-04T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="1a568cb7f44ef30d1ede99af3cb3b195"/>
-    <x v="4"/>
-    <d v="2025-05-04T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="f491d1b2d2de653272191e07a51777b5"/>
-    <x v="10"/>
-    <d v="2025-05-04T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="437.67"/>
-    <n v="455.8"/>
-    <n v="893.47"/>
-    <n v="1893.47"/>
-  </r>
-  <r>
-    <s v="c84bf0208198bb54847bb833764ad0a0"/>
-    <x v="8"/>
-    <d v="2025-05-05T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="36d603b1f2ec25d9364364f358c233ff"/>
-    <x v="15"/>
-    <d v="2025-05-05T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="e0c519d4ea255960aadb13f0459ad371"/>
-    <x v="2"/>
-    <d v="2025-05-05T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="f1051574caadd35ee75a5d2318483251"/>
-    <x v="5"/>
-    <d v="2025-05-05T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="c490f96dca265a78f225d85c18001972"/>
-    <x v="9"/>
-    <d v="2025-05-05T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="26d1ab669e2aa759c2980184d010d99f"/>
-    <x v="9"/>
-    <d v="2025-05-05T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="7da08d702734c3b1d1c42863d3d2d4d5"/>
-    <x v="10"/>
-    <d v="2025-05-05T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="616.55999999999995"/>
-    <n v="682.82"/>
-    <n v="1299.3800000000001"/>
-    <n v="2299.38"/>
-  </r>
-  <r>
-    <s v="2d7b38ad15c9fabfbdfcc5df9db35f67"/>
-    <x v="6"/>
-    <d v="2025-05-05T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="616.55999999999995"/>
-    <n v="682.82"/>
-    <n v="1299.3800000000001"/>
-    <n v="2299.38"/>
-  </r>
-  <r>
-    <s v="02ced5c9d599a5162d92c8755dca60c5"/>
-    <x v="7"/>
-    <d v="2025-05-06T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="bd78d1d9073b09b17486299465997eef"/>
-    <x v="16"/>
-    <d v="2025-05-06T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="46bccc2fa7d60052aa41257bff578102"/>
-    <x v="8"/>
-    <d v="2025-05-06T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="aa403f9ec7d4cfad1e56f56e3c9a2d99"/>
-    <x v="3"/>
-    <d v="2025-05-06T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="d3a2f3f66aeaad823850840ef69dbe7b"/>
-    <x v="13"/>
-    <d v="2025-05-06T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="036d7d6932bd3ceed707bb061e2919a9"/>
-    <x v="13"/>
-    <d v="2025-05-06T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="fecc6f73d94936c107cb9dcf0b707c53"/>
-    <x v="10"/>
-    <d v="2025-05-06T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="259.02999999999997"/>
-    <n v="287.5"/>
-    <n v="546.53"/>
-    <n v="1546.53"/>
-  </r>
-  <r>
-    <s v="d22a969568ff1cdcd013fecd622b8320"/>
-    <x v="1"/>
-    <d v="2025-05-07T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="f4acd330e5378aed37a03d8a5329c5f4"/>
-    <x v="2"/>
-    <d v="2025-05-07T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="c82494aecbb5ac83932c985739656199"/>
-    <x v="3"/>
-    <d v="2025-05-07T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="96b9eb0dcc6ae3e20ba91ad579abd50a"/>
-    <x v="4"/>
-    <d v="2025-05-07T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="726e340bb5f33e93813065bd208b9329"/>
-    <x v="4"/>
-    <d v="2025-05-07T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="a2b597f41bcd565bee0d66048f1cf2cd"/>
-    <x v="14"/>
-    <d v="2025-05-07T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Дерматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="2.85"/>
-    <n v="0"/>
-    <n v="14.2"/>
-    <n v="17.05"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="17.05"/>
-  </r>
-  <r>
-    <s v="ea264b099cdb059278d68cff6d52a7bb"/>
-    <x v="6"/>
-    <d v="2025-05-07T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="110.88"/>
-    <n v="1748.31"/>
-    <n v="1859.19"/>
-    <n v="2859.19"/>
-  </r>
-  <r>
-    <s v="e48be8806809258128e381c8bd29cd0f"/>
-    <x v="17"/>
-    <d v="2025-05-08T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="3e7593e692564b148957338069b8ff90"/>
-    <x v="1"/>
-    <d v="2025-05-08T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="f7387c5e54abae39a03207f3e3bdf90b"/>
-    <x v="15"/>
-    <d v="2025-05-08T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="45b862da1708409ee760fa3fccf21a65"/>
-    <x v="3"/>
-    <d v="2025-05-08T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="0600e57f4c9aea0685467c245c29cfd9"/>
-    <x v="9"/>
-    <d v="2025-05-08T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="63700b18a45377411d82534821ad9252"/>
-    <x v="9"/>
-    <d v="2025-05-08T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="0f96973ffaad51c1736727af1bcddd9b"/>
-    <x v="5"/>
-    <d v="2025-05-08T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Стоматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="6.8384999999999998"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="6.8384999999999998"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="6.8384999999999998"/>
-  </r>
-  <r>
-    <s v="23a685b1aa81186db513bc5bf1036cc7"/>
-    <x v="6"/>
-    <d v="2025-05-08T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="518.29"/>
-    <n v="1680.01"/>
-    <n v="2198.3000000000002"/>
-    <n v="3198.3"/>
-  </r>
-  <r>
-    <s v="611589c50ef4b34a1ed45130e43a4202"/>
-    <x v="7"/>
-    <d v="2025-05-09T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="2034090fa0fbc259b2c681b1a6c50e16"/>
-    <x v="16"/>
-    <d v="2025-05-09T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="a92c20da0897ede148fb1911a9504e53"/>
-    <x v="10"/>
-    <d v="2025-05-09T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="4c88fff561e4be1975945359a9ecfb4a"/>
-    <x v="5"/>
-    <d v="2025-05-09T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="b0702f156edbf674329db824c87cc3af"/>
-    <x v="13"/>
-    <d v="2025-05-09T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="31327d80f9e8cba25133d1f990f40f4f"/>
-    <x v="13"/>
-    <d v="2025-05-09T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="ddf8f657aa458629649b3f810e8717df"/>
-    <x v="10"/>
-    <d v="2025-05-09T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="443.62"/>
-    <n v="806.58"/>
-    <n v="1250.2"/>
-    <n v="2250.1999999999998"/>
-  </r>
-  <r>
-    <s v="1d827b7fdc96a6dec4aff36e3fa9becc"/>
-    <x v="17"/>
-    <d v="2025-05-10T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="32657c2c7338f268f4abc08275defde6"/>
-    <x v="8"/>
-    <d v="2025-05-10T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="eb401863651c3cf0e7c3ebac4a6d3f71"/>
-    <x v="2"/>
-    <d v="2025-05-10T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="228d5ddcd23f6ecdcbb7ba60dade0141"/>
-    <x v="12"/>
-    <d v="2025-05-10T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="98f248bc1019c146092bc8d11fc73eb6"/>
-    <x v="3"/>
-    <d v="2025-05-10T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="6aa63549a1a300db5a8ba40859ddc906"/>
-    <x v="4"/>
-    <d v="2025-05-10T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="e04615c5b68300eb739f0fe4c0b0f42e"/>
-    <x v="4"/>
-    <d v="2025-05-10T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="e94308f761d9a0b2fe649374e086a717"/>
-    <x v="5"/>
-    <d v="2025-05-10T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Стоматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="2.4704000000000002"/>
-    <n v="45"/>
-    <n v="0"/>
-    <n v="47.470399999999998"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="47.470399999999998"/>
-  </r>
-  <r>
-    <s v="188590b541f0c33c3cb802a08d5cd294"/>
-    <x v="14"/>
-    <d v="2025-05-10T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Дерматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="11.7"/>
-    <n v="11.7"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="11.7"/>
-  </r>
-  <r>
-    <s v="d97c634116d20906df3946e7e774762d"/>
-    <x v="6"/>
-    <d v="2025-05-10T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="473.25"/>
-    <n v="1449.55"/>
-    <n v="1922.8"/>
-    <n v="2922.8"/>
-  </r>
-  <r>
-    <s v="3e1d1b947027d9d69e4b10e9d3d5d3da"/>
-    <x v="11"/>
-    <d v="2025-05-11T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="adead603e24892b5afd59e470766f926"/>
-    <x v="2"/>
-    <d v="2025-05-11T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="aceb96d070feb16be24c9fe3a49a03fb"/>
-    <x v="8"/>
-    <d v="2025-05-11T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="3fad0d677e402634cbb8bdf4d22d0d43"/>
-    <x v="5"/>
-    <d v="2025-05-11T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="80e2bcf1ea4e26e048913af467365420"/>
-    <x v="13"/>
-    <d v="2025-05-11T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="57ae497b3eeb874c79f12eb175a379f2"/>
-    <x v="13"/>
-    <d v="2025-05-11T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="63afaa7fb6817d63f9ac3272d78d1d8a"/>
-    <x v="10"/>
-    <d v="2025-05-11T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="131.85"/>
-    <n v="443"/>
-    <n v="574.85"/>
-    <n v="1574.85"/>
-  </r>
-  <r>
-    <s v="823c5dd5e0173717f6ebbcd5a545fd56"/>
-    <x v="8"/>
-    <d v="2025-05-12T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="7e3fec5ee053a8f72bbb2b66a4d2cfce"/>
-    <x v="15"/>
-    <d v="2025-05-12T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="2475a41de727b882c72df6cc2fd115b4"/>
-    <x v="15"/>
-    <d v="2025-05-12T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="66f20916a7d533710c5c006d0d9f3de2"/>
-    <x v="5"/>
-    <d v="2025-05-12T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="cbdd16e0f52fe5962e318d76fbdf8a41"/>
-    <x v="9"/>
-    <d v="2025-05-12T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="10bf80102731e6d2b6d7cc088f616801"/>
-    <x v="9"/>
-    <d v="2025-05-12T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="0e5cd2f148d8a849142cef6bce528de2"/>
-    <x v="10"/>
-    <d v="2025-05-12T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="447.19"/>
-    <n v="889.08"/>
-    <n v="1336.27"/>
-    <n v="2336.27"/>
-  </r>
-  <r>
-    <s v="c87fc775b2470384c34b28f3beddf8cb"/>
-    <x v="6"/>
-    <d v="2025-05-12T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="447.19"/>
-    <n v="889.08"/>
-    <n v="1336.27"/>
-    <n v="2336.27"/>
-  </r>
-  <r>
-    <s v="b116b8b7af2f1aeab0a742b6e9008ee4"/>
-    <x v="0"/>
-    <d v="2025-05-13T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="e8d015e979d36a52461bf3dce844fea9"/>
-    <x v="7"/>
-    <d v="2025-05-13T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="0155a3c471d26236b5df0e47b2ce6fb1"/>
-    <x v="2"/>
-    <d v="2025-05-13T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="0ebf72cad8a2cdf51d4cb0f812996947"/>
-    <x v="3"/>
-    <d v="2025-05-13T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="7fd6003e4502f0d0175a106ba7b56dad"/>
-    <x v="4"/>
-    <d v="2025-05-13T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="8ae631f66fd39ed355b50792cb212525"/>
-    <x v="4"/>
-    <d v="2025-05-13T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="24e6de69e1d609e3b4274d7828d0de5c"/>
-    <x v="10"/>
-    <d v="2025-05-13T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="330.86"/>
-    <n v="589.22"/>
-    <n v="920.08"/>
-    <n v="1920.08"/>
-  </r>
-  <r>
-    <s v="8d746f6d3575d74c6ea9359ff8598ab8"/>
-    <x v="1"/>
-    <d v="2025-05-14T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="145f2d16239e8f4010625e8557db3f39"/>
-    <x v="8"/>
-    <d v="2025-05-14T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="6967f94f217fdec48900d84dc353fdb5"/>
-    <x v="3"/>
-    <d v="2025-05-14T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="898ddce3be46a9d45f26b9e97017dcfd"/>
-    <x v="13"/>
-    <d v="2025-05-14T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="4a2c366b0cb6cd148dbee74d9158366e"/>
-    <x v="13"/>
-    <d v="2025-05-14T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="70d585d92637f9dcabd61ba040f2d7b4"/>
-    <x v="14"/>
-    <d v="2025-05-14T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Дерматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <s v="59274c25856f6247963cbe499a9cade3"/>
-    <x v="6"/>
-    <d v="2025-05-14T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="255.29"/>
-    <n v="492"/>
-    <n v="747.29"/>
-    <n v="1747.29"/>
-  </r>
-  <r>
-    <s v="94aed7b443d6167e2623d6bdb5086fb4"/>
-    <x v="17"/>
-    <d v="2025-05-15T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="5b871c973622662dea97eaf496bc3439"/>
-    <x v="1"/>
-    <d v="2025-05-15T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="5e5de3058493a15bab307abf596cd938"/>
-    <x v="1"/>
-    <d v="2025-05-15T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="bf96c0fc9f08bb3904524042e88790e7"/>
-    <x v="3"/>
-    <d v="2025-05-15T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="2cdc785eabfb8ba681ebfcc793e53330"/>
-    <x v="9"/>
-    <d v="2025-05-15T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="450c921ae2fc7fc54809359b4906466e"/>
-    <x v="9"/>
-    <d v="2025-05-15T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="87f0cce17aec2502a4694e4063f208b8"/>
-    <x v="5"/>
-    <d v="2025-05-15T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Стоматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <s v="e398b2abf1fb9d1026b5138ba6dfdd7b"/>
-    <x v="6"/>
-    <d v="2025-05-15T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="357.35"/>
-    <n v="1679.35"/>
-    <n v="2036.7"/>
-    <n v="3036.7"/>
-  </r>
-  <r>
-    <s v="e191a54ff5feb14b876ec63e36213775"/>
-    <x v="11"/>
-    <d v="2025-05-16T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="2b5cb1740483273c32f279796fcf7d0e"/>
-    <x v="7"/>
-    <d v="2025-05-16T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="fb5be4f28cc10d70912c9a89c2095fb0"/>
-    <x v="16"/>
-    <d v="2025-05-16T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="6d14273f7ad2a7fc38a7f6d38a592e9f"/>
-    <x v="5"/>
-    <d v="2025-05-16T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="796e913ad75f669c06508a6b861ec619"/>
-    <x v="4"/>
-    <d v="2025-05-16T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="91934e0a16a49ff7642e8957587951dc"/>
-    <x v="4"/>
-    <d v="2025-05-16T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="39403a82b2a403f32a80b376c5f56a46"/>
-    <x v="10"/>
-    <d v="2025-05-16T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="487.54"/>
-    <n v="747.62"/>
-    <n v="1235.1600000000001"/>
-    <n v="2235.16"/>
-  </r>
-  <r>
-    <s v="5309fc518916e8e6c8695674b3b471b2"/>
-    <x v="0"/>
-    <d v="2025-05-17T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="f9d299b2f768c6a58d62882a3697330d"/>
-    <x v="16"/>
-    <d v="2025-05-17T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="1d688241ae0ee30de7810e85b29b3c39"/>
-    <x v="8"/>
-    <d v="2025-05-17T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="1a4fe1c2cfb0893bd66e7a74b9bf6f2e"/>
-    <x v="3"/>
-    <d v="2025-05-17T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="6c1bd560d1e4307bd17b9e9d51d5c9fd"/>
-    <x v="13"/>
-    <d v="2025-05-17T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="2009cba63ad6514e15a361dd5ba89c75"/>
-    <x v="13"/>
-    <d v="2025-05-17T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="ee1170d07294ece9804a6bd84a189ada"/>
-    <x v="5"/>
-    <d v="2025-05-17T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Стоматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="1.5029999999999999"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1.5029999999999999"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1.5029999999999999"/>
-  </r>
-  <r>
-    <s v="82764e1080a46ca43b141f4ebaf60976"/>
-    <x v="14"/>
-    <d v="2025-05-17T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Дерматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="8"/>
-    <n v="36.1"/>
-    <n v="44.1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="44.1"/>
-  </r>
-  <r>
-    <s v="bb87ff531ab954b87707d05536933e6b"/>
-    <x v="10"/>
-    <d v="2025-05-17T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="408.07"/>
-    <n v="2140.09"/>
-    <n v="2548.16"/>
-    <n v="3548.16"/>
-  </r>
-  <r>
-    <s v="e367c3935827263e5b86af5e0e3ec264"/>
-    <x v="17"/>
-    <d v="2025-05-18T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="483eeb4b82639692637d91862ea1d7c2"/>
-    <x v="2"/>
-    <d v="2025-05-18T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="102ab7709df1ce5acf3466e8a0240f3b"/>
-    <x v="15"/>
-    <d v="2025-05-18T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="00ddb53c252c925db18e4c56c353b79e"/>
-    <x v="5"/>
-    <d v="2025-05-18T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="3a4de813cecea3d1e4e256f7eb71e562"/>
-    <x v="9"/>
-    <d v="2025-05-18T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="58986e1791aa964debde89f062f62c22"/>
-    <x v="9"/>
-    <d v="2025-05-18T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="1530efecf326b2f2840efe940ac4d87a"/>
-    <x v="10"/>
-    <d v="2025-05-18T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="182.8"/>
-    <n v="202.67"/>
-    <n v="385.47"/>
-    <n v="1385.47"/>
-  </r>
-  <r>
-    <s v="9a935aff570ffd2e0cbb36ce8007ff4d"/>
-    <x v="8"/>
-    <d v="2025-05-19T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="d4f033e4a23227905c4e1b02a611a806"/>
-    <x v="15"/>
-    <d v="2025-05-19T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="51048bb47d95c6deaa54a4fc8221802c"/>
-    <x v="16"/>
-    <d v="2025-05-19T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="94eacb25d2c878b73b332754baffca30"/>
-    <x v="5"/>
-    <d v="2025-05-19T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="5967f1bcb16e6aa18a1cf747ff5105cd"/>
-    <x v="4"/>
-    <d v="2025-05-19T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="f11e91669bd1e7c4133d98e3d6749ac0"/>
-    <x v="4"/>
-    <d v="2025-05-19T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="cd46dd6cc29ca3ec96539491ce8e96f6"/>
-    <x v="10"/>
-    <d v="2025-05-19T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="492.43"/>
-    <n v="1199.5"/>
-    <n v="1691.93"/>
-    <n v="2691.93"/>
-  </r>
-  <r>
-    <s v="8a39198349870ff43fef000901297bd4"/>
-    <x v="2"/>
-    <d v="2025-05-19T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="492.43"/>
-    <n v="1199.5"/>
-    <n v="1691.93"/>
-    <n v="2691.93"/>
-  </r>
-  <r>
-    <s v="bdea56b6969309347b3afe542048a0b7"/>
-    <x v="7"/>
-    <d v="2025-05-20T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="a03e9875ab6a91cefa1697eaa9a67acb"/>
-    <x v="1"/>
-    <d v="2025-05-20T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="540965362d189946554b7a86927efe75"/>
-    <x v="8"/>
-    <d v="2025-05-20T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="eac3981380af626e89d2efec3be89cba"/>
-    <x v="5"/>
-    <d v="2025-05-20T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="a4fd14f5566d24de36a78ff09cddc9a1"/>
-    <x v="13"/>
-    <d v="2025-05-20T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="0b783bccf3a30c80ccb37a5c351430cc"/>
-    <x v="13"/>
-    <d v="2025-05-20T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="3dbc006f17be619bb18e4ab495124cf2"/>
-    <x v="6"/>
-    <d v="2025-05-20T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="73.75"/>
-    <n v="230.27"/>
-    <n v="304.02"/>
-    <n v="1304.02"/>
-  </r>
-  <r>
-    <s v="073a58e3039dedbad9e45fad7287c20c"/>
-    <x v="7"/>
-    <d v="2025-05-21T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="f7d57dc33ccecbc5ce9f18d16690b15f"/>
-    <x v="15"/>
-    <d v="2025-05-21T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="bc3893d1778d636dd833cd2d151d29fc"/>
-    <x v="15"/>
-    <d v="2025-05-21T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="4096f7b06ffa99f25e6fd895072a760f"/>
-    <x v="3"/>
-    <d v="2025-05-21T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="415dd6723c594d60bf600bd1f3918b2c"/>
-    <x v="9"/>
-    <d v="2025-05-21T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="1af128181efed294d34907da8f25c16e"/>
-    <x v="9"/>
-    <d v="2025-05-21T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="351cdadee1f4a6ad7b91ec6f7422d065"/>
-    <x v="14"/>
-    <d v="2025-05-21T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Дерматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <s v="7197c698ff475b9265ef0a722e1b1362"/>
-    <x v="6"/>
-    <d v="2025-05-21T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="389.33"/>
-    <n v="861.72"/>
-    <n v="1251.05"/>
-    <n v="2251.0500000000002"/>
-  </r>
-  <r>
-    <s v="0ea5dd634046b801ae20c476d51f767f"/>
-    <x v="17"/>
-    <d v="2025-05-22T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="3afaf93861bbc4ffe172848d2257d4d5"/>
-    <x v="2"/>
-    <d v="2025-05-22T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="c9f64c8b9be85228cb5d1da11dc50446"/>
-    <x v="2"/>
-    <d v="2025-05-22T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="835510294cd08a7a1f86b0e788ae91b7"/>
-    <x v="3"/>
-    <d v="2025-05-22T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="45c5e35bf34747755a0c16d6aeeef6d1"/>
-    <x v="4"/>
-    <d v="2025-05-22T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="a02d7ecdcec7642f2e9da4c920b99ec7"/>
-    <x v="4"/>
-    <d v="2025-05-22T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="197e594eb0802492a9bc954d80f863b4"/>
-    <x v="5"/>
-    <d v="2025-05-22T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Стоматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <s v="9fefb58e7c4249640cda5ac33b426a74"/>
-    <x v="10"/>
-    <d v="2025-05-22T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="354.05"/>
-    <n v="1157.1600000000001"/>
-    <n v="1511.21"/>
-    <n v="2511.21"/>
-  </r>
-  <r>
-    <s v="cba0fabed432e6835d0137dcae6b5b19"/>
-    <x v="17"/>
-    <d v="2025-05-23T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="464d110d93a9931dfeef7ec451d76116"/>
-    <x v="1"/>
-    <d v="2025-05-23T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="82c57ddeff448eed2cc8c73c7cdd3938"/>
-    <x v="8"/>
-    <d v="2025-05-23T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="47800d1df97a9bc1101881013277f215"/>
-    <x v="5"/>
-    <d v="2025-05-23T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="813ad59a78c1e3f48918afa14e3d61ec"/>
-    <x v="13"/>
-    <d v="2025-05-23T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="dac836a5669b2bbc9a2143e37bedd6d9"/>
-    <x v="9"/>
-    <d v="2025-05-23T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="43e64927f1171662d05f817e5b9e51d7"/>
-    <x v="10"/>
-    <d v="2025-05-23T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="248.7"/>
-    <n v="557"/>
-    <n v="805.7"/>
-    <n v="1805.7"/>
-  </r>
-  <r>
-    <s v="c802423a3bd0475987c860ab918bfe58"/>
-    <x v="0"/>
-    <d v="2025-05-24T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="51ed77e4ce16efe113f4963e4f8b8065"/>
-    <x v="11"/>
-    <d v="2025-05-24T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="3194663c51de9e9772fdb86005c39800"/>
-    <x v="15"/>
-    <d v="2025-05-24T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="e42175ebcea4df7aa37751ad64d3387b"/>
-    <x v="12"/>
-    <d v="2025-05-24T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="d3bc6d5fc5c42fefb0fa2fc0840f2d9d"/>
-    <x v="3"/>
-    <d v="2025-05-24T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="cd16b26090e4b7396c53869f7304f733"/>
-    <x v="13"/>
-    <d v="2025-05-24T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="7bf59de140b7e5401769de883a613c8e"/>
-    <x v="13"/>
-    <d v="2025-05-24T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="944c7b187476ec8433e75d37b9b1ec95"/>
-    <x v="5"/>
-    <d v="2025-05-24T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Стоматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0.56000000000000005"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0.56000000000000005"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0.56000000000000005"/>
-  </r>
-  <r>
-    <s v="b042c3fd6780139b926a747e8ff976b7"/>
-    <x v="14"/>
-    <d v="2025-05-24T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Дерматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="11.7011"/>
-    <n v="11.7011"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="11.7011"/>
-  </r>
-  <r>
-    <s v="7f2370d619d147384ec0d9a2e6d80503"/>
-    <x v="6"/>
-    <d v="2025-05-24T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="444.54"/>
-    <n v="2551.7600000000002"/>
-    <n v="2996.3"/>
-    <n v="3996.3"/>
-  </r>
-  <r>
-    <s v="15a2d4d88d7777c2d4eb92a26e2a21c1"/>
-    <x v="0"/>
-    <d v="2025-05-25T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="00e4de0762be3dfd61496087f456b672"/>
-    <x v="16"/>
-    <d v="2025-05-25T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="4f7d7269f58a457702d8cc2900574244"/>
-    <x v="8"/>
-    <d v="2025-05-25T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="6cfe996529ac7961b662fb6a1b754c6e"/>
-    <x v="5"/>
-    <d v="2025-05-25T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="799b03d9c278abdad0745d7b32655c6b"/>
-    <x v="4"/>
-    <d v="2025-05-25T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="8ea3b33b52b1eb745d58d64032b9c656"/>
-    <x v="4"/>
-    <d v="2025-05-25T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="af57dcbfef4e466a90cdc44b2a4d5264"/>
-    <x v="6"/>
-    <d v="2025-05-25T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="124.26"/>
-    <n v="269.67"/>
-    <n v="393.93"/>
-    <n v="1393.93"/>
-  </r>
-  <r>
-    <s v="227a550e129c78e9ecc89d151328d8be"/>
-    <x v="0"/>
-    <d v="2025-05-26T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="ddd89e63a9d7c500486745d8c8c427ea"/>
-    <x v="17"/>
-    <d v="2025-05-26T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="b7f2307e48a6e5a23f892b52f2ce78ea"/>
-    <x v="16"/>
-    <d v="2025-05-26T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="360d80d2143cea6df9f7c044e7b68864"/>
-    <x v="5"/>
-    <d v="2025-05-26T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="5b6632172ca2214b3b5451a95708a65d"/>
-    <x v="13"/>
-    <d v="2025-05-26T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="08a622b8cda78f0b7ed98b2e63abe0ea"/>
-    <x v="9"/>
-    <d v="2025-05-26T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="a8a23202b2f9e820ed60ab20254e8a24"/>
-    <x v="10"/>
-    <d v="2025-05-26T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="264.85000000000002"/>
-    <n v="194.5"/>
-    <n v="459.35"/>
-    <n v="1459.35"/>
-  </r>
-  <r>
-    <s v="6ca0434db39e1b1122fe15235477279c"/>
-    <x v="2"/>
-    <d v="2025-05-26T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="264.85000000000002"/>
-    <n v="194.5"/>
-    <n v="459.35"/>
-    <n v="1459.35"/>
-  </r>
-  <r>
-    <s v="2d36e28d6fa73418c5013c46d350f769"/>
-    <x v="1"/>
-    <d v="2025-05-27T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="b128efdb2c580f679ac8083af2915b93"/>
-    <x v="16"/>
-    <d v="2025-05-27T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="639429f165f1bfd2dc400579baf2a8f7"/>
-    <x v="2"/>
-    <d v="2025-05-27T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="660162adb05f98aaf85231d3611aee27"/>
-    <x v="3"/>
-    <d v="2025-05-27T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="ea62f1a481693a7b77be6a51a2158a6f"/>
-    <x v="13"/>
-    <d v="2025-05-27T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="4ae6e2f3deb956ff522bfcda42763e92"/>
-    <x v="13"/>
-    <d v="2025-05-27T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="c8841a501ccc34c88d2f756f24e42684"/>
-    <x v="10"/>
-    <d v="2025-05-27T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="429.45"/>
-    <n v="1147.03"/>
-    <n v="1576.48"/>
-    <n v="2576.48"/>
-  </r>
-  <r>
-    <s v="507e78db220ba0d60a4d5b69a15130a1"/>
-    <x v="11"/>
-    <d v="2025-05-28T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="deff1d15554c4540cdf9b94cadda2286"/>
-    <x v="15"/>
-    <d v="2025-05-28T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="1f5f35a9dc49c0101013ccea78e0ff9a"/>
-    <x v="2"/>
-    <d v="2025-05-28T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="5e95eb063664baa37ee1a6fd43434c6a"/>
-    <x v="3"/>
-    <d v="2025-05-28T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="700f822be6acdacde15aecdea80371a3"/>
-    <x v="4"/>
-    <d v="2025-05-28T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="3d7db171e163e3e287e8bebef92bd075"/>
-    <x v="4"/>
-    <d v="2025-05-28T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="d768970a8f9fc185178a8029965d379c"/>
-    <x v="14"/>
-    <d v="2025-05-28T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Дерматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <s v="9e9b56546e363f97e6197847b14b4be2"/>
-    <x v="6"/>
-    <d v="2025-05-28T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="358.38"/>
-    <n v="873.94"/>
-    <n v="1232.32"/>
-    <n v="2232.3200000000002"/>
-  </r>
-  <r>
-    <s v="3e1636bf5759d527e1be445e6efb1e40"/>
-    <x v="17"/>
-    <d v="2025-05-29T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="7f3ce8d1c901aee460147672c755841e"/>
-    <x v="15"/>
-    <d v="2025-05-29T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="c0b6f4fc8e486f933c7e22d0199c5138"/>
-    <x v="16"/>
-    <d v="2025-05-29T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="834907c931127917780d95a2f40f4ba2"/>
-    <x v="3"/>
-    <d v="2025-05-29T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="cd3ab71fbb7954bd41cb08564be07620"/>
-    <x v="13"/>
-    <d v="2025-05-29T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="d35efbb526b2cde45e11da3b280d85cb"/>
-    <x v="9"/>
-    <d v="2025-05-29T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="cc33ba8fb7e5463887028dc4b93b7527"/>
-    <x v="5"/>
-    <d v="2025-05-29T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Стоматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <s v="788a11bcc6f2483ad795d4cec8cafcbe"/>
-    <x v="10"/>
-    <d v="2025-05-29T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="136.75"/>
-    <n v="1108"/>
-    <n v="1244.75"/>
-    <n v="2244.75"/>
-  </r>
-  <r>
-    <s v="106c5eb822faf6e5c1ec2768df0f152c"/>
-    <x v="11"/>
-    <d v="2025-05-30T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="15eef9470b9da50b1482cd00bdcb474e"/>
-    <x v="1"/>
-    <d v="2025-05-30T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="32710b8211e0bb4ba207f24256c52979"/>
-    <x v="2"/>
-    <d v="2025-05-30T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="efdc3b0f1311fbf638279bdbbcffc6db"/>
-    <x v="5"/>
-    <d v="2025-05-30T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="2794bc5552c810b3ebc5b7670c080fe6"/>
-    <x v="13"/>
-    <d v="2025-05-30T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="e776b9225684f40bb7080749cf738435"/>
-    <x v="13"/>
-    <d v="2025-05-30T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="1600"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1600"/>
-  </r>
-  <r>
-    <s v="44e7e10a50dc02ebb046c433ebf619d4"/>
-    <x v="10"/>
-    <d v="2025-05-30T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="336.94"/>
-    <n v="859.3"/>
-    <n v="1196.24"/>
-    <n v="2196.2399999999998"/>
-  </r>
-  <r>
-    <s v="d6d4d48c1cfccf887219bee7b017c1f7"/>
-    <x v="1"/>
-    <d v="2025-05-31T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="53fe0c3720b4926f7975733682aafcdf"/>
-    <x v="11"/>
-    <d v="2025-05-31T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="5c56e0f53a2c6c11e66eaaf5c6bbb1d7"/>
-    <x v="12"/>
-    <d v="2025-05-31T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="a29319cbcb550ac349a0245829101628"/>
-    <x v="12"/>
-    <d v="2025-05-31T00:00:00"/>
-    <s v="Асистент"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="800"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="800"/>
-  </r>
-  <r>
-    <s v="6fc78d3f6b6d263a44b30c4b7fd1aac3"/>
-    <x v="3"/>
-    <d v="2025-05-31T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="Терапевт"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2300"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2300"/>
-  </r>
-  <r>
-    <s v="f0953e0dc8a597768ed106d90e1fe773"/>
-    <x v="4"/>
-    <d v="2025-05-31T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="55fb17dca16dac5b5c21806d19bb63ec"/>
-    <x v="4"/>
-    <d v="2025-05-31T00:00:00"/>
-    <s v="Лікар"/>
-    <s v="ВРІТ"/>
-    <s v="Ніч"/>
-    <s v="12:00"/>
-    <n v="2000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2000"/>
-  </r>
-  <r>
-    <s v="24950bbf48a72b0aef42ebcf27141ca9"/>
-    <x v="5"/>
-    <d v="2025-05-31T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Стоматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="40"/>
-    <n v="0"/>
-    <n v="40"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="40"/>
-  </r>
-  <r>
-    <s v="4befaf0a1a56d8bc89979b1a9088b8c5"/>
-    <x v="14"/>
-    <d v="2025-05-31T00:00:00"/>
-    <s v="Лікар ВП"/>
-    <s v="Дерматолог"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="7.8"/>
-    <n v="23.56"/>
-    <n v="31.36"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="31.36"/>
-  </r>
-  <r>
-    <s v="d1dcbee90b1947b987b371b32c583af3"/>
-    <x v="10"/>
-    <d v="2025-05-31T00:00:00"/>
-    <s v="Фронт"/>
-    <s v="Реєстратор"/>
-    <s v="День"/>
-    <s v="12:00"/>
-    <n v="1000"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="816.46"/>
-    <n v="3120.41"/>
-    <n v="3936.87"/>
-    <n v="4936.87"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{213A1556-238D-4792-AE18-E752C5AD4E04}" name="Сводная таблица1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:G22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="19">
-        <item x="10"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="9"/>
-        <item x="4"/>
-        <item x="17"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-    <i i="4">
-      <x v="4"/>
-    </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
-  </colItems>
-  <dataFields count="6">
-    <dataField name="Сумма по полю ВсьогоЗаЗміну" fld="15" baseField="0" baseItem="0" numFmtId="3"/>
-    <dataField name="Сумма по полю Ставка" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Сумма по полю КолективнаПремія_Зоомагазин" fld="12" baseField="0" baseItem="0"/>
-    <dataField name="Сумма по полю КолективнаПремія_Послуги" fld="13" baseField="0" baseItem="0"/>
-    <dataField name="Сумма по полю КолективнаПремія_Всього" fld="14" baseField="0" baseItem="0"/>
-    <dataField name="Количество по полю shift_uuid" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="1">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="6">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3C222874-6566-497A-9CD5-61762D992F4F}" name="Таблица1" displayName="Таблица1" ref="A1:P243" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="4" tableBorderDxfId="5">
-  <autoFilter ref="A1:P243" xr:uid="{3C222874-6566-497A-9CD5-61762D992F4F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2BAFE460-EC8B-4E14-9CF7-F4A00AF56A46}" name="Таблица1" displayName="Таблица1" ref="A1:P243" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
+  <autoFilter ref="A1:P243" xr:uid="{2BAFE460-EC8B-4E14-9CF7-F4A00AF56A46}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Стоматолог"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{72C3B116-5CE1-4773-8876-A8CA909A231A}" name="shift_uuid"/>
-    <tableColumn id="2" xr3:uid="{C815CD17-18B3-42F6-B14B-5D3492BE661F}" name="Прізвище"/>
-    <tableColumn id="3" xr3:uid="{BE653C8A-AA69-4175-B0D2-3CAB23535351}" name="ДатаЗміни" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{4DF8B690-FFC8-40FC-96EC-B65835EB744B}" name="Посада"/>
-    <tableColumn id="5" xr3:uid="{3A2BC6AD-2186-4E62-AD80-A3D131052F84}" name="Відділення"/>
-    <tableColumn id="6" xr3:uid="{337F200B-7919-4E2A-8E0B-E6480AB3DE1F}" name="ТипЗміни"/>
-    <tableColumn id="7" xr3:uid="{B2334FF8-2AAA-49F6-8D8F-2AFB097C8BDA}" name="ТривалістьЗміни"/>
-    <tableColumn id="8" xr3:uid="{52CD8178-6B3B-4952-8F8F-A83CDB1F35E7}" name="Ставка"/>
-    <tableColumn id="9" xr3:uid="{511E772D-6624-4CFA-85B0-697F7474B49E}" name="Премія_Зоомагазин"/>
-    <tableColumn id="10" xr3:uid="{CDA3119B-CB1A-4CF4-BED3-A7292567294C}" name="Премія_Медикаменти"/>
-    <tableColumn id="11" xr3:uid="{546E79E7-E5FF-4A5C-A791-9419F57D2D6B}" name="Премія_Послуги"/>
-    <tableColumn id="12" xr3:uid="{1E182B3E-DA7B-4222-9D4D-8D1B7A2DC0BD}" name="Премія_Всього"/>
-    <tableColumn id="13" xr3:uid="{D762B49E-95B9-4D65-B54B-F88A00B1867A}" name="КолективнаПремія_Зоомагазин"/>
-    <tableColumn id="14" xr3:uid="{29F2E43F-CB2D-4AB4-88B2-07F378460B06}" name="КолективнаПремія_Послуги"/>
-    <tableColumn id="15" xr3:uid="{1DCBA750-45B3-4C0F-B30E-06761276E587}" name="КолективнаПремія_Всього"/>
-    <tableColumn id="16" xr3:uid="{AE183580-8F29-4162-8056-E529C890B8D9}" name="ВсьогоЗаЗміну"/>
+    <tableColumn id="1" xr3:uid="{6E926C86-FD03-4888-9696-410661E65EB3}" name="shift_uuid"/>
+    <tableColumn id="2" xr3:uid="{B07EEBA4-41EB-4EFC-81C9-EC9A92D1BBAE}" name="Прізвище"/>
+    <tableColumn id="3" xr3:uid="{B972AE76-B88F-4052-8F0B-8E6BCFECBDDB}" name="ДатаЗміни" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{5167A630-1492-4E14-8066-BE8BE3DA1070}" name="Посада"/>
+    <tableColumn id="5" xr3:uid="{FBB79F83-7061-4084-AFBD-4DD195726CC9}" name="Відділення"/>
+    <tableColumn id="6" xr3:uid="{45F0985E-8311-4BE8-8C01-06748A73925E}" name="ТипЗміни"/>
+    <tableColumn id="7" xr3:uid="{A3E91F6C-0C51-4A9B-A108-C996A70A62BD}" name="ТривалістьЗміни"/>
+    <tableColumn id="8" xr3:uid="{14F595FC-35E9-4712-BDC0-2A3616942126}" name="Ставка"/>
+    <tableColumn id="9" xr3:uid="{410CEFDB-48D4-4772-A752-4939F384722B}" name="Премія_Зоомагазин"/>
+    <tableColumn id="10" xr3:uid="{12F0C1BB-E8F5-4809-9EB2-5814128E4A2C}" name="Премія_Медикаменти"/>
+    <tableColumn id="11" xr3:uid="{9717AA5D-A4F8-447F-81ED-36CE5995BBA6}" name="Премія_Послуги"/>
+    <tableColumn id="12" xr3:uid="{44418DC7-B65A-4D26-9187-7A56F485B577}" name="Премія_Всього"/>
+    <tableColumn id="13" xr3:uid="{344DDA57-FBE9-44E7-83E3-95317C3E8460}" name="КолективнаПремія_Зоомагазин"/>
+    <tableColumn id="14" xr3:uid="{F18480B1-5C25-4374-900E-D0332956F551}" name="КолективнаПремія_Послуги"/>
+    <tableColumn id="15" xr3:uid="{6CC4C510-D431-4146-B5C6-A7098B3919E7}" name="КолективнаПремія_Всього"/>
+    <tableColumn id="16" xr3:uid="{CB23ACEC-7778-4F12-9FBB-0816FF985EE5}" name="ВсьогоЗаЗміну"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5973,500 +1324,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08081C3-A82D-4494-82B3-A5CEAC6DBC60}">
-  <dimension ref="A3:G22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="11.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:7" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="5">
-        <v>47394.909999999996</v>
-      </c>
-      <c r="C4" s="4">
-        <v>20800</v>
-      </c>
-      <c r="D4" s="4">
-        <v>7508.52</v>
-      </c>
-      <c r="E4" s="4">
-        <v>19086.39</v>
-      </c>
-      <c r="F4" s="4">
-        <v>26594.91</v>
-      </c>
-      <c r="G4" s="4">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="5">
-        <v>39100</v>
-      </c>
-      <c r="C5" s="4">
-        <v>39100</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="5">
-        <v>36800</v>
-      </c>
-      <c r="C6" s="4">
-        <v>36800</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="5">
-        <v>7200</v>
-      </c>
-      <c r="C7" s="4">
-        <v>7200</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="5">
-        <v>5600</v>
-      </c>
-      <c r="C8" s="4">
-        <v>5600</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="5">
-        <v>171.77030000000002</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="5">
-        <v>8800</v>
-      </c>
-      <c r="C10" s="4">
-        <v>8800</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="5">
-        <v>4800</v>
-      </c>
-      <c r="C11" s="4">
-        <v>4800</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="5">
-        <v>9600</v>
-      </c>
-      <c r="C12" s="4">
-        <v>9600</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="5">
-        <v>34000</v>
-      </c>
-      <c r="C13" s="4">
-        <v>34000</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="5">
-        <v>44000</v>
-      </c>
-      <c r="C14" s="4">
-        <v>44000</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="5">
-        <v>6400</v>
-      </c>
-      <c r="C15" s="4">
-        <v>6400</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="5">
-        <v>28097.778400000003</v>
-      </c>
-      <c r="C16" s="4">
-        <v>28000</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="5">
-        <v>33287.120000000003</v>
-      </c>
-      <c r="C17" s="4">
-        <v>13000</v>
-      </c>
-      <c r="D17" s="4">
-        <v>4377.41</v>
-      </c>
-      <c r="E17" s="4">
-        <v>15909.710000000003</v>
-      </c>
-      <c r="F17" s="4">
-        <v>20287.12</v>
-      </c>
-      <c r="G17" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5">
-        <v>6400</v>
-      </c>
-      <c r="C18" s="4">
-        <v>6400</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="5">
-        <v>14551.28</v>
-      </c>
-      <c r="C19" s="4">
-        <v>12400</v>
-      </c>
-      <c r="D19" s="4">
-        <v>757.28</v>
-      </c>
-      <c r="E19" s="4">
-        <v>1394</v>
-      </c>
-      <c r="F19" s="4">
-        <v>2151.2800000000002</v>
-      </c>
-      <c r="G19" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="5">
-        <v>5600</v>
-      </c>
-      <c r="C20" s="4">
-        <v>5600</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0</v>
-      </c>
-      <c r="F20" s="4">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="5">
-        <v>10400</v>
-      </c>
-      <c r="C21" s="4">
-        <v>10400</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B22" s="5">
-        <v>342202.85869999998</v>
-      </c>
-      <c r="C22" s="4">
-        <v>292900</v>
-      </c>
-      <c r="D22" s="4">
-        <v>12643.210000000003</v>
-      </c>
-      <c r="E22" s="4">
-        <v>36390.1</v>
-      </c>
-      <c r="F22" s="4">
-        <v>49033.31</v>
-      </c>
-      <c r="G22" s="4">
-        <v>242</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P243"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.88671875" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.88671875" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" customWidth="1"/>
-    <col min="11" max="11" width="17.5546875" customWidth="1"/>
-    <col min="12" max="12" width="16.21875" customWidth="1"/>
-    <col min="13" max="13" width="31.21875" customWidth="1"/>
-    <col min="14" max="14" width="27.88671875" customWidth="1"/>
-    <col min="15" max="15" width="26.6640625" customWidth="1"/>
-    <col min="16" max="16" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="9.21875" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
+    <col min="9" max="9" width="20.5546875" customWidth="1"/>
+    <col min="10" max="10" width="22.5546875" customWidth="1"/>
+    <col min="11" max="11" width="17.109375" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="30.77734375" customWidth="1"/>
+    <col min="14" max="14" width="27.33203125" customWidth="1"/>
+    <col min="15" max="15" width="26.21875" customWidth="1"/>
+    <col min="16" max="16" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -6519,7 +1395,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6569,7 +1445,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -6619,7 +1495,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -6669,7 +1545,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -6719,7 +1595,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -6769,7 +1645,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -6851,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>4010</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>4010</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -6866,10 +1742,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -6910,16 +1786,16 @@
         <v>208.34</v>
       </c>
       <c r="N9">
-        <v>2501.23</v>
+        <v>750.37</v>
       </c>
       <c r="O9">
-        <v>2709.57</v>
+        <v>958.71</v>
       </c>
       <c r="P9">
-        <v>3709.57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1958.71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -6969,7 +1845,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -7019,7 +1895,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -7069,7 +1945,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -7119,7 +1995,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -7169,7 +2045,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -7219,7 +2095,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>51</v>
       </c>
@@ -7260,16 +2136,16 @@
         <v>223.37</v>
       </c>
       <c r="N16">
-        <v>873.83</v>
+        <v>262.14999999999998</v>
       </c>
       <c r="O16">
-        <v>1097.2</v>
+        <v>485.52</v>
       </c>
       <c r="P16">
-        <v>2097.1999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1485.52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -7319,7 +2195,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -7369,7 +2245,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -7419,7 +2295,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -7469,7 +2345,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>59</v>
       </c>
@@ -7519,7 +2395,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -7569,7 +2445,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -7645,16 +2521,16 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>1.4065000000000001</v>
+        <v>14.065</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>3128</v>
       </c>
       <c r="L24">
-        <v>1.4065000000000001</v>
+        <v>3142.0650000000001</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -7666,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.4065000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+        <v>3142.0650000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -7698,13 +2574,13 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>9.75</v>
+        <v>19.5</v>
       </c>
       <c r="K25">
-        <v>46.109200000000001</v>
+        <v>2074.9140000000002</v>
       </c>
       <c r="L25">
-        <v>55.859200000000001</v>
+        <v>2094.4140000000002</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -7716,10 +2592,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>55.859200000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2094.4140000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -7760,16 +2636,16 @@
         <v>460.33</v>
       </c>
       <c r="N26">
-        <v>1625.28</v>
+        <v>487.58</v>
       </c>
       <c r="O26">
-        <v>2085.61</v>
+        <v>947.91</v>
       </c>
       <c r="P26">
-        <v>3085.61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1947.91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>68</v>
       </c>
@@ -7819,7 +2695,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -7869,7 +2745,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -7919,7 +2795,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -7969,7 +2845,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -8019,7 +2895,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -8069,7 +2945,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -8110,16 +2986,16 @@
         <v>437.67</v>
       </c>
       <c r="N33">
-        <v>455.8</v>
+        <v>136.74</v>
       </c>
       <c r="O33">
-        <v>893.47</v>
+        <v>574.41000000000008</v>
       </c>
       <c r="P33">
-        <v>1893.47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1574.41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -8169,7 +3045,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -8219,7 +3095,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -8269,7 +3145,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -8319,7 +3195,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -8369,7 +3245,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -8419,7 +3295,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -8460,16 +3336,16 @@
         <v>616.55999999999995</v>
       </c>
       <c r="N40">
-        <v>682.82</v>
+        <v>204.85</v>
       </c>
       <c r="O40">
-        <v>1299.3800000000001</v>
+        <v>821.41</v>
       </c>
       <c r="P40">
-        <v>2299.38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1821.41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -8510,16 +3386,16 @@
         <v>616.55999999999995</v>
       </c>
       <c r="N41">
-        <v>682.82</v>
+        <v>204.85</v>
       </c>
       <c r="O41">
-        <v>1299.3800000000001</v>
+        <v>821.41</v>
       </c>
       <c r="P41">
-        <v>2299.38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1821.41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -8569,7 +3445,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -8619,7 +3495,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -8669,7 +3545,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -8719,7 +3595,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>89</v>
       </c>
@@ -8769,7 +3645,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>90</v>
       </c>
@@ -8819,7 +3695,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>91</v>
       </c>
@@ -8860,16 +3736,16 @@
         <v>259.02999999999997</v>
       </c>
       <c r="N48">
-        <v>287.5</v>
+        <v>86.25</v>
       </c>
       <c r="O48">
-        <v>546.53</v>
+        <v>345.28</v>
       </c>
       <c r="P48">
-        <v>1546.53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1345.28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>92</v>
       </c>
@@ -8919,7 +3795,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>93</v>
       </c>
@@ -8969,7 +3845,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>94</v>
       </c>
@@ -9019,7 +3895,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>95</v>
       </c>
@@ -9069,7 +3945,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>96</v>
       </c>
@@ -9119,7 +3995,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>97</v>
       </c>
@@ -9145,16 +4021,16 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>2.85</v>
+        <v>28.5</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54">
-        <v>14.2</v>
+        <v>639</v>
       </c>
       <c r="L54">
-        <v>17.05</v>
+        <v>667.5</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -9166,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>17.05</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+        <v>667.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>98</v>
       </c>
@@ -9210,16 +4086,16 @@
         <v>110.88</v>
       </c>
       <c r="N55">
-        <v>1748.31</v>
+        <v>524.49</v>
       </c>
       <c r="O55">
-        <v>1859.19</v>
+        <v>635.37</v>
       </c>
       <c r="P55">
-        <v>2859.19</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1635.37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>99</v>
       </c>
@@ -9269,7 +4145,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>101</v>
       </c>
@@ -9319,7 +4195,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>102</v>
       </c>
@@ -9369,7 +4245,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>103</v>
       </c>
@@ -9419,7 +4295,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>104</v>
       </c>
@@ -9469,7 +4345,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>105</v>
       </c>
@@ -9545,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>6.8384999999999998</v>
+        <v>68.385000000000005</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>3705</v>
       </c>
       <c r="L62">
-        <v>6.8384999999999998</v>
+        <v>3773.3850000000002</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -9566,10 +4442,10 @@
         <v>0</v>
       </c>
       <c r="P62">
-        <v>6.8384999999999998</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+        <v>3773.3850000000002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>107</v>
       </c>
@@ -9610,16 +4486,16 @@
         <v>518.29</v>
       </c>
       <c r="N63">
-        <v>1680.01</v>
+        <v>504</v>
       </c>
       <c r="O63">
-        <v>2198.3000000000002</v>
+        <v>1022.29</v>
       </c>
       <c r="P63">
-        <v>3198.3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2022.29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>108</v>
       </c>
@@ -9669,7 +4545,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>109</v>
       </c>
@@ -9719,7 +4595,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>110</v>
       </c>
@@ -9769,7 +4645,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>111</v>
       </c>
@@ -9819,7 +4695,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>112</v>
       </c>
@@ -9869,7 +4745,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>113</v>
       </c>
@@ -9919,7 +4795,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>114</v>
       </c>
@@ -9960,16 +4836,16 @@
         <v>443.62</v>
       </c>
       <c r="N70">
-        <v>806.58</v>
+        <v>241.97</v>
       </c>
       <c r="O70">
-        <v>1250.2</v>
+        <v>685.59</v>
       </c>
       <c r="P70">
-        <v>2250.1999999999998</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1685.59</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>115</v>
       </c>
@@ -10019,7 +4895,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>116</v>
       </c>
@@ -10069,7 +4945,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>117</v>
       </c>
@@ -10119,7 +4995,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>118</v>
       </c>
@@ -10169,7 +5045,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>119</v>
       </c>
@@ -10219,7 +5095,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -10269,7 +5145,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>121</v>
       </c>
@@ -10345,16 +5221,16 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>2.4704000000000002</v>
+        <v>24.704000000000001</v>
       </c>
       <c r="J78">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>4772.2879999999996</v>
       </c>
       <c r="L78">
-        <v>47.470399999999998</v>
+        <v>4886.9919999999993</v>
       </c>
       <c r="M78">
         <v>0</v>
@@ -10366,10 +5242,10 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>47.470399999999998</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+        <v>4886.9919999999993</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>123</v>
       </c>
@@ -10401,10 +5277,10 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>11.7</v>
+        <v>526.5</v>
       </c>
       <c r="L79">
-        <v>11.7</v>
+        <v>526.5</v>
       </c>
       <c r="M79">
         <v>0</v>
@@ -10416,10 +5292,10 @@
         <v>0</v>
       </c>
       <c r="P79">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+        <v>526.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>124</v>
       </c>
@@ -10460,16 +5336,16 @@
         <v>473.25</v>
       </c>
       <c r="N80">
-        <v>1449.55</v>
+        <v>434.86</v>
       </c>
       <c r="O80">
-        <v>1922.8</v>
+        <v>908.11</v>
       </c>
       <c r="P80">
-        <v>2922.8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1908.11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>125</v>
       </c>
@@ -10519,7 +5395,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>126</v>
       </c>
@@ -10569,7 +5445,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>127</v>
       </c>
@@ -10619,7 +5495,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>128</v>
       </c>
@@ -10669,7 +5545,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -10719,7 +5595,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>130</v>
       </c>
@@ -10769,7 +5645,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>131</v>
       </c>
@@ -10810,16 +5686,16 @@
         <v>131.85</v>
       </c>
       <c r="N87">
-        <v>443</v>
+        <v>132.9</v>
       </c>
       <c r="O87">
-        <v>574.85</v>
+        <v>264.75</v>
       </c>
       <c r="P87">
-        <v>1574.85</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1264.75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>132</v>
       </c>
@@ -10869,7 +5745,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>133</v>
       </c>
@@ -10919,7 +5795,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>134</v>
       </c>
@@ -10969,7 +5845,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>135</v>
       </c>
@@ -11019,7 +5895,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>136</v>
       </c>
@@ -11069,7 +5945,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>137</v>
       </c>
@@ -11119,7 +5995,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>138</v>
       </c>
@@ -11160,16 +6036,16 @@
         <v>447.19</v>
       </c>
       <c r="N94">
-        <v>889.08</v>
+        <v>266.72000000000003</v>
       </c>
       <c r="O94">
-        <v>1336.27</v>
+        <v>713.91000000000008</v>
       </c>
       <c r="P94">
-        <v>2336.27</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1713.91</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>139</v>
       </c>
@@ -11210,16 +6086,16 @@
         <v>447.19</v>
       </c>
       <c r="N95">
-        <v>889.08</v>
+        <v>266.72000000000003</v>
       </c>
       <c r="O95">
-        <v>1336.27</v>
+        <v>713.91000000000008</v>
       </c>
       <c r="P95">
-        <v>2336.27</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1713.91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>140</v>
       </c>
@@ -11269,7 +6145,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>141</v>
       </c>
@@ -11319,7 +6195,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>142</v>
       </c>
@@ -11369,7 +6245,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>143</v>
       </c>
@@ -11419,7 +6295,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>144</v>
       </c>
@@ -11469,7 +6345,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>145</v>
       </c>
@@ -11519,7 +6395,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>146</v>
       </c>
@@ -11560,16 +6436,16 @@
         <v>330.86</v>
       </c>
       <c r="N102">
-        <v>589.22</v>
+        <v>176.77</v>
       </c>
       <c r="O102">
-        <v>920.08</v>
+        <v>507.63</v>
       </c>
       <c r="P102">
-        <v>1920.08</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1507.63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -11619,7 +6495,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>148</v>
       </c>
@@ -11669,7 +6545,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>149</v>
       </c>
@@ -11719,7 +6595,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>150</v>
       </c>
@@ -11769,7 +6645,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>151</v>
       </c>
@@ -11819,7 +6695,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>152</v>
       </c>
@@ -11869,7 +6745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -11910,16 +6786,16 @@
         <v>255.29</v>
       </c>
       <c r="N109">
-        <v>492</v>
+        <v>147.6</v>
       </c>
       <c r="O109">
-        <v>747.29</v>
+        <v>402.89</v>
       </c>
       <c r="P109">
-        <v>1747.29</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1402.89</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>154</v>
       </c>
@@ -11969,7 +6845,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>155</v>
       </c>
@@ -12019,7 +6895,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>156</v>
       </c>
@@ -12069,7 +6945,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>157</v>
       </c>
@@ -12119,7 +6995,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>158</v>
       </c>
@@ -12169,7 +7045,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>159</v>
       </c>
@@ -12251,10 +7127,10 @@
         <v>0</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>2924</v>
       </c>
       <c r="L116">
-        <v>0</v>
+        <v>2924</v>
       </c>
       <c r="M116">
         <v>0</v>
@@ -12266,10 +7142,10 @@
         <v>0</v>
       </c>
       <c r="P116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>161</v>
       </c>
@@ -12310,16 +7186,16 @@
         <v>357.35</v>
       </c>
       <c r="N117">
-        <v>1679.35</v>
+        <v>503.81</v>
       </c>
       <c r="O117">
-        <v>2036.7</v>
+        <v>861.16000000000008</v>
       </c>
       <c r="P117">
-        <v>3036.7</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1861.16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>162</v>
       </c>
@@ -12369,7 +7245,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>163</v>
       </c>
@@ -12419,7 +7295,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>164</v>
       </c>
@@ -12469,7 +7345,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>165</v>
       </c>
@@ -12519,7 +7395,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>166</v>
       </c>
@@ -12569,7 +7445,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>167</v>
       </c>
@@ -12619,7 +7495,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>168</v>
       </c>
@@ -12660,16 +7536,16 @@
         <v>487.54</v>
       </c>
       <c r="N124">
-        <v>747.62</v>
+        <v>224.29</v>
       </c>
       <c r="O124">
-        <v>1235.1600000000001</v>
+        <v>711.83</v>
       </c>
       <c r="P124">
-        <v>2235.16</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1711.83</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>169</v>
       </c>
@@ -12719,7 +7595,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>170</v>
       </c>
@@ -12769,7 +7645,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>171</v>
       </c>
@@ -12819,7 +7695,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>172</v>
       </c>
@@ -12869,7 +7745,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>173</v>
       </c>
@@ -12919,7 +7795,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>174</v>
       </c>
@@ -12995,16 +7871,16 @@
         <v>0</v>
       </c>
       <c r="I131">
-        <v>1.5029999999999999</v>
+        <v>15.03</v>
       </c>
       <c r="J131">
         <v>0</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>3288</v>
       </c>
       <c r="L131">
-        <v>1.5029999999999999</v>
+        <v>3303.03</v>
       </c>
       <c r="M131">
         <v>0</v>
@@ -13016,10 +7892,10 @@
         <v>0</v>
       </c>
       <c r="P131">
-        <v>1.5029999999999999</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+        <v>3303.03</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>176</v>
       </c>
@@ -13048,13 +7924,13 @@
         <v>0</v>
       </c>
       <c r="J132">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K132">
-        <v>36.1</v>
+        <v>1624.5</v>
       </c>
       <c r="L132">
-        <v>44.1</v>
+        <v>1640.5</v>
       </c>
       <c r="M132">
         <v>0</v>
@@ -13066,10 +7942,10 @@
         <v>0</v>
       </c>
       <c r="P132">
-        <v>44.1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1640.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>177</v>
       </c>
@@ -13110,16 +7986,16 @@
         <v>408.07</v>
       </c>
       <c r="N133">
-        <v>2140.09</v>
+        <v>642.03</v>
       </c>
       <c r="O133">
-        <v>2548.16</v>
+        <v>1050.0999999999999</v>
       </c>
       <c r="P133">
-        <v>3548.16</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2050.1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>178</v>
       </c>
@@ -13169,7 +8045,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>179</v>
       </c>
@@ -13219,7 +8095,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>180</v>
       </c>
@@ -13269,7 +8145,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>181</v>
       </c>
@@ -13319,7 +8195,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>182</v>
       </c>
@@ -13369,7 +8245,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>183</v>
       </c>
@@ -13419,7 +8295,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>184</v>
       </c>
@@ -13460,16 +8336,16 @@
         <v>182.8</v>
       </c>
       <c r="N140">
-        <v>202.67</v>
+        <v>60.8</v>
       </c>
       <c r="O140">
-        <v>385.47</v>
+        <v>243.6</v>
       </c>
       <c r="P140">
-        <v>1385.47</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1243.5999999999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>185</v>
       </c>
@@ -13519,7 +8395,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>186</v>
       </c>
@@ -13569,7 +8445,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>187</v>
       </c>
@@ -13619,7 +8495,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>188</v>
       </c>
@@ -13669,7 +8545,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>189</v>
       </c>
@@ -13719,7 +8595,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>190</v>
       </c>
@@ -13769,7 +8645,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>191</v>
       </c>
@@ -13810,16 +8686,16 @@
         <v>492.43</v>
       </c>
       <c r="N147">
-        <v>1199.5</v>
+        <v>359.85</v>
       </c>
       <c r="O147">
-        <v>1691.93</v>
+        <v>852.28</v>
       </c>
       <c r="P147">
-        <v>2691.93</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1852.28</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>192</v>
       </c>
@@ -13860,16 +8736,16 @@
         <v>492.43</v>
       </c>
       <c r="N148">
-        <v>1199.5</v>
+        <v>359.85</v>
       </c>
       <c r="O148">
-        <v>1691.93</v>
+        <v>852.28</v>
       </c>
       <c r="P148">
-        <v>2691.93</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1852.28</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>193</v>
       </c>
@@ -13919,7 +8795,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>194</v>
       </c>
@@ -13969,7 +8845,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>195</v>
       </c>
@@ -14019,7 +8895,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>196</v>
       </c>
@@ -14069,7 +8945,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>197</v>
       </c>
@@ -14119,7 +8995,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>198</v>
       </c>
@@ -14169,7 +9045,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>199</v>
       </c>
@@ -14210,16 +9086,16 @@
         <v>73.75</v>
       </c>
       <c r="N155">
-        <v>230.27</v>
+        <v>69.08</v>
       </c>
       <c r="O155">
-        <v>304.02</v>
+        <v>142.83000000000001</v>
       </c>
       <c r="P155">
-        <v>1304.02</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1142.83</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>200</v>
       </c>
@@ -14269,7 +9145,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>201</v>
       </c>
@@ -14319,7 +9195,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>202</v>
       </c>
@@ -14369,7 +9245,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>203</v>
       </c>
@@ -14419,7 +9295,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>204</v>
       </c>
@@ -14469,7 +9345,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>205</v>
       </c>
@@ -14519,7 +9395,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>206</v>
       </c>
@@ -14569,7 +9445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>207</v>
       </c>
@@ -14610,16 +9486,16 @@
         <v>389.33</v>
       </c>
       <c r="N163">
-        <v>861.72</v>
+        <v>258.52</v>
       </c>
       <c r="O163">
-        <v>1251.05</v>
+        <v>647.84999999999991</v>
       </c>
       <c r="P163">
-        <v>2251.0500000000002</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1647.85</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>208</v>
       </c>
@@ -14669,7 +9545,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>209</v>
       </c>
@@ -14719,7 +9595,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>210</v>
       </c>
@@ -14769,7 +9645,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>211</v>
       </c>
@@ -14819,7 +9695,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>212</v>
       </c>
@@ -14869,7 +9745,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>213</v>
       </c>
@@ -14951,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>3555</v>
       </c>
       <c r="L170">
-        <v>0</v>
+        <v>3555</v>
       </c>
       <c r="M170">
         <v>0</v>
@@ -14966,10 +9842,10 @@
         <v>0</v>
       </c>
       <c r="P170">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
+        <v>3555</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>215</v>
       </c>
@@ -15010,16 +9886,16 @@
         <v>354.05</v>
       </c>
       <c r="N171">
-        <v>1157.1600000000001</v>
+        <v>347.15</v>
       </c>
       <c r="O171">
-        <v>1511.21</v>
+        <v>701.2</v>
       </c>
       <c r="P171">
-        <v>2511.21</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1701.2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>216</v>
       </c>
@@ -15069,7 +9945,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>217</v>
       </c>
@@ -15119,7 +9995,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>218</v>
       </c>
@@ -15169,7 +10045,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>219</v>
       </c>
@@ -15219,7 +10095,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>220</v>
       </c>
@@ -15269,7 +10145,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>221</v>
       </c>
@@ -15319,7 +10195,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>222</v>
       </c>
@@ -15360,16 +10236,16 @@
         <v>248.7</v>
       </c>
       <c r="N178">
-        <v>557</v>
+        <v>167.1</v>
       </c>
       <c r="O178">
-        <v>805.7</v>
+        <v>415.8</v>
       </c>
       <c r="P178">
-        <v>1805.7</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1415.8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>223</v>
       </c>
@@ -15419,7 +10295,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>224</v>
       </c>
@@ -15469,7 +10345,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>225</v>
       </c>
@@ -15519,7 +10395,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>226</v>
       </c>
@@ -15569,7 +10445,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>227</v>
       </c>
@@ -15619,7 +10495,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>228</v>
       </c>
@@ -15669,7 +10545,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>229</v>
       </c>
@@ -15745,16 +10621,16 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>0.56000000000000005</v>
+        <v>5.6</v>
       </c>
       <c r="J186">
         <v>0</v>
       </c>
       <c r="K186">
-        <v>0</v>
+        <v>6392</v>
       </c>
       <c r="L186">
-        <v>0.56000000000000005</v>
+        <v>6397.6</v>
       </c>
       <c r="M186">
         <v>0</v>
@@ -15766,10 +10642,10 @@
         <v>0</v>
       </c>
       <c r="P186">
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
+        <v>6397.6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>231</v>
       </c>
@@ -15801,10 +10677,10 @@
         <v>0</v>
       </c>
       <c r="K187">
-        <v>11.7011</v>
+        <v>526.54949999999997</v>
       </c>
       <c r="L187">
-        <v>11.7011</v>
+        <v>526.54949999999997</v>
       </c>
       <c r="M187">
         <v>0</v>
@@ -15816,10 +10692,10 @@
         <v>0</v>
       </c>
       <c r="P187">
-        <v>11.7011</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
+        <v>526.54949999999997</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>232</v>
       </c>
@@ -15860,16 +10736,16 @@
         <v>444.54</v>
       </c>
       <c r="N188">
-        <v>2551.7600000000002</v>
+        <v>765.53</v>
       </c>
       <c r="O188">
-        <v>2996.3</v>
+        <v>1210.07</v>
       </c>
       <c r="P188">
-        <v>3996.3</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2210.0700000000002</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>233</v>
       </c>
@@ -15919,7 +10795,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>234</v>
       </c>
@@ -15969,7 +10845,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>235</v>
       </c>
@@ -16019,7 +10895,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>236</v>
       </c>
@@ -16069,7 +10945,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>237</v>
       </c>
@@ -16119,7 +10995,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>238</v>
       </c>
@@ -16169,7 +11045,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>239</v>
       </c>
@@ -16210,16 +11086,16 @@
         <v>124.26</v>
       </c>
       <c r="N195">
-        <v>269.67</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="O195">
-        <v>393.93</v>
+        <v>205.16</v>
       </c>
       <c r="P195">
-        <v>1393.93</v>
-      </c>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1205.1600000000001</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>240</v>
       </c>
@@ -16269,7 +11145,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>241</v>
       </c>
@@ -16319,7 +11195,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>242</v>
       </c>
@@ -16369,7 +11245,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>243</v>
       </c>
@@ -16419,7 +11295,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>244</v>
       </c>
@@ -16469,7 +11345,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>245</v>
       </c>
@@ -16519,7 +11395,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>246</v>
       </c>
@@ -16560,16 +11436,16 @@
         <v>264.85000000000002</v>
       </c>
       <c r="N202">
-        <v>194.5</v>
+        <v>58.35</v>
       </c>
       <c r="O202">
-        <v>459.35</v>
+        <v>323.2</v>
       </c>
       <c r="P202">
-        <v>1459.35</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1323.2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>247</v>
       </c>
@@ -16610,16 +11486,16 @@
         <v>264.85000000000002</v>
       </c>
       <c r="N203">
-        <v>194.5</v>
+        <v>58.35</v>
       </c>
       <c r="O203">
-        <v>459.35</v>
+        <v>323.2</v>
       </c>
       <c r="P203">
-        <v>1459.35</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1323.2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>248</v>
       </c>
@@ -16669,7 +11545,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>249</v>
       </c>
@@ -16719,7 +11595,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>250</v>
       </c>
@@ -16769,7 +11645,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>251</v>
       </c>
@@ -16819,7 +11695,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>252</v>
       </c>
@@ -16869,7 +11745,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>253</v>
       </c>
@@ -16919,7 +11795,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>254</v>
       </c>
@@ -16960,16 +11836,16 @@
         <v>429.45</v>
       </c>
       <c r="N210">
-        <v>1147.03</v>
+        <v>344.11</v>
       </c>
       <c r="O210">
-        <v>1576.48</v>
+        <v>773.56</v>
       </c>
       <c r="P210">
-        <v>2576.48</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1773.56</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>255</v>
       </c>
@@ -17019,7 +11895,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>256</v>
       </c>
@@ -17069,7 +11945,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>257</v>
       </c>
@@ -17119,7 +11995,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>258</v>
       </c>
@@ -17169,7 +12045,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>259</v>
       </c>
@@ -17219,7 +12095,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>260</v>
       </c>
@@ -17269,7 +12145,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>261</v>
       </c>
@@ -17319,7 +12195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>262</v>
       </c>
@@ -17360,16 +12236,16 @@
         <v>358.38</v>
       </c>
       <c r="N218">
-        <v>873.94</v>
+        <v>262.18</v>
       </c>
       <c r="O218">
-        <v>1232.32</v>
+        <v>620.55999999999995</v>
       </c>
       <c r="P218">
-        <v>2232.3200000000002</v>
-      </c>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1620.56</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>263</v>
       </c>
@@ -17419,7 +12295,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>264</v>
       </c>
@@ -17469,7 +12345,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>265</v>
       </c>
@@ -17519,7 +12395,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>266</v>
       </c>
@@ -17569,7 +12445,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>267</v>
       </c>
@@ -17619,7 +12495,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>268</v>
       </c>
@@ -17701,10 +12577,10 @@
         <v>0</v>
       </c>
       <c r="K225">
-        <v>0</v>
+        <v>3855</v>
       </c>
       <c r="L225">
-        <v>0</v>
+        <v>3855</v>
       </c>
       <c r="M225">
         <v>0</v>
@@ -17716,10 +12592,10 @@
         <v>0</v>
       </c>
       <c r="P225">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.3">
+        <v>3855</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>270</v>
       </c>
@@ -17760,16 +12636,16 @@
         <v>136.75</v>
       </c>
       <c r="N226">
-        <v>1108</v>
+        <v>332.4</v>
       </c>
       <c r="O226">
-        <v>1244.75</v>
+        <v>469.15</v>
       </c>
       <c r="P226">
-        <v>2244.75</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1469.15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>271</v>
       </c>
@@ -17819,7 +12695,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>272</v>
       </c>
@@ -17869,7 +12745,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>273</v>
       </c>
@@ -17919,7 +12795,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>274</v>
       </c>
@@ -17969,7 +12845,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>275</v>
       </c>
@@ -18019,7 +12895,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>276</v>
       </c>
@@ -18069,7 +12945,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>277</v>
       </c>
@@ -18110,16 +12986,16 @@
         <v>336.94</v>
       </c>
       <c r="N233">
-        <v>859.3</v>
+        <v>257.79000000000002</v>
       </c>
       <c r="O233">
-        <v>1196.24</v>
+        <v>594.73</v>
       </c>
       <c r="P233">
-        <v>2196.2399999999998</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1594.73</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>278</v>
       </c>
@@ -18169,7 +13045,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>279</v>
       </c>
@@ -18219,7 +13095,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>280</v>
       </c>
@@ -18269,7 +13145,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>281</v>
       </c>
@@ -18319,7 +13195,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>282</v>
       </c>
@@ -18369,7 +13245,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>283</v>
       </c>
@@ -18419,7 +13295,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>284</v>
       </c>
@@ -18498,13 +13374,13 @@
         <v>0</v>
       </c>
       <c r="J241">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K241">
-        <v>0</v>
+        <v>9272</v>
       </c>
       <c r="L241">
-        <v>40</v>
+        <v>9352</v>
       </c>
       <c r="M241">
         <v>0</v>
@@ -18516,10 +13392,10 @@
         <v>0</v>
       </c>
       <c r="P241">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.3">
+        <v>9352</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>286</v>
       </c>
@@ -18548,13 +13424,13 @@
         <v>0</v>
       </c>
       <c r="J242">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="K242">
-        <v>23.56</v>
+        <v>1060.2</v>
       </c>
       <c r="L242">
-        <v>31.36</v>
+        <v>1075.8</v>
       </c>
       <c r="M242">
         <v>0</v>
@@ -18566,10 +13442,10 @@
         <v>0</v>
       </c>
       <c r="P242">
-        <v>31.36</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1075.8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>287</v>
       </c>
@@ -18610,13 +13486,13 @@
         <v>816.46</v>
       </c>
       <c r="N243">
-        <v>3120.41</v>
+        <v>936.12</v>
       </c>
       <c r="O243">
-        <v>3936.87</v>
+        <v>1752.58</v>
       </c>
       <c r="P243">
-        <v>4936.87</v>
+        <v>2752.58</v>
       </c>
     </row>
   </sheetData>
